--- a/JsonConverter/ExcelFiles/DNFieldObject.xlsx
+++ b/JsonConverter/ExcelFiles/DNFieldObject.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fileVersion appName="HCell" lastEdited="12.0" lowestEdited="12.0" rupBuild="0.535"/>
+  <x:fileVersion appName="HCell" lastEdited="10.0" lowestEdited="10.0" rupBuild="0.12458"/>
   <x:workbookPr date1904="0" showBorderUnselectedTables="1" filterPrivacy="0" promptedSolutions="0" showInkAnnotation="1" backupFile="0" saveExternalLinkValues="1" codeName="ThisWorkbook" hidePivotFieldList="0" allowRefreshQuery="0" publishItems="0" checkCompatibility="0" autoCompressPictures="1" refreshAllConnections="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\0_NRUnityProjects\UnityBasic_6\JsonConverter\ExcelFiles\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\0_NRUnityProjects\2DMainProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <x:bookViews>
-    <x:workbookView xWindow="0" yWindow="0" windowWidth="4294934950" windowHeight="6150"/>
+    <x:workbookView xWindow="0" yWindow="0" windowWidth="22788" windowHeight="8520"/>
   </x:bookViews>
   <x:sheets>
     <x:sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId4"/>
@@ -19,105 +19,159 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="33">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="51">
+  <x:si>
+    <x:t>2DPrefab/DropItem_ManaBallPink</x:t>
+  </x:si>
+  <x:si>
+    <x:t>파랑경험치볼</x:t>
+  </x:si>
+  <x:si>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dropItem_manaballorange_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>소량 경험치</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_ManaBallPink_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2DPrefab/Harvest_Potato</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2DPrefab/Harvest_Corn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2DPrefab/DropItem_Gold</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>int[]</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10,1000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10,100</x:t>
+  </x:si>
+  <x:si>
+    <x:t>드랍된 금화</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
   <x:si>
     <x:t>Harvest</x:t>
   </x:si>
   <x:si>
-    <x:t>10,1000</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10,100</x:t>
-  </x:si>
-  <x:si>
-    <x:t>int[]</x:t>
-  </x:si>
-  <x:si>
-    <x:t>드랍된 금화</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
     <x:t>Name</x:t>
   </x:si>
   <x:si>
+    <x:t>dropItem_gold_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FieldObjectType</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DropCountRange</x:t>
+  </x:si>
+  <x:si>
+    <x:t>우선 프리팹으로 구현하자!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DropItemDataId</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Potato_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>몬스터 설명 (도감용)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>harv_potate_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2DPrefab/DropItem_ManaBallBlue</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대량 경험치</x:t>
+  </x:si>
+  <x:si>
+    <x:t>주황경험치볼</x:t>
+  </x:si>
+  <x:si>
     <x:t>캐릭터 고유 ID</x:t>
   </x:si>
   <x:si>
+    <x:t>Item_Corn_1</x:t>
+  </x:si>
+  <x:si>
     <x:t>Item_Gold_1</x:t>
   </x:si>
   <x:si>
-    <x:t>Item_Corn_1</x:t>
-  </x:si>
-  <x:si>
     <x:t>Description</x:t>
   </x:si>
   <x:si>
     <x:t>IconPath</x:t>
   </x:si>
   <x:si>
+    <x:t>DropItem</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PrefabPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>필드 채집용 감자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>필드 채집용 옥수수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>harv_corn_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>금화</x:t>
+  </x:si>
+  <x:si>
+    <x:t>감자</x:t>
+  </x:si>
+  <x:si>
     <x:t>옥수수</x:t>
   </x:si>
   <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>harv_potate_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Potato_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dropItem_gold_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FieldObjectType</x:t>
-  </x:si>
-  <x:si>
-    <x:t>몬스터 설명 (도감용)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DropCountRange</x:t>
-  </x:si>
-  <x:si>
-    <x:t>우선 프리팹으로 구현하자!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DropItemDataId</x:t>
-  </x:si>
-  <x:si>
-    <x:t>감자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>금화</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DropItem</x:t>
-  </x:si>
-  <x:si>
-    <x:t>harv_corn_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PrefabPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>필드 채집용 옥수수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>필드 채집용 감자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2DPrefab/Harvest_Potato</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2DPrefab/DropItem_Gold</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2DPrefab/Harvest_Corn</x:t>
+    <x:t>dropItem_manaballblue_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_ManaBallOrange_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dropItem_manaballpink_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_ManaBallBlue_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2DPrefab/DropItem_ManaBallOrange</x:t>
+  </x:si>
+  <x:si>
+    <x:t>분홍경험치볼</x:t>
+  </x:si>
+  <x:si>
+    <x:t>중량 경험치</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ManaPoints</x:t>
+  </x:si>
+  <x:si>
+    <x:t>마나량</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -230,16 +284,16 @@
   <x:borders count="3">
     <x:border>
       <x:left>
-        <x:color rgb="ff000000"/>
+        <x:color auto="1"/>
       </x:left>
       <x:right>
-        <x:color rgb="ff000000"/>
+        <x:color auto="1"/>
       </x:right>
       <x:top>
         <x:color auto="1"/>
       </x:top>
       <x:bottom>
-        <x:color rgb="ff000000"/>
+        <x:color auto="1"/>
       </x:bottom>
     </x:border>
     <x:border>
@@ -277,8 +331,8 @@
     </x:xf>
   </x:cellStyleXfs>
   <x:cellXfs count="29">
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <x:alignment horizontal="general" vertical="bottom"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="left" vertical="bottom"/>
@@ -967,114 +1021,120 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetPr codeName="Sheet1">
-    <x:outlinePr applyStyles="0" summaryBelow="0" summaryRight="1" showOutlineSymbols="1"/>
-  </x:sheetPr>
+  <x:sheetPr codeName="Sheet1"/>
   <x:dimension ref="A1:R34"/>
   <x:sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15" customHeight="1"/>
   <x:cols>
-    <x:col min="1" max="2" width="19.453125" style="3" customWidth="1"/>
+    <x:col min="1" max="1" width="25.44921875" style="3" bestFit="1" customWidth="1"/>
+    <x:col min="2" max="2" width="19.453125" style="3" customWidth="1"/>
     <x:col min="3" max="3" width="19.54296875" style="3" customWidth="1"/>
     <x:col min="4" max="4" width="50.7265625" style="3" customWidth="1"/>
     <x:col min="5" max="6" width="50.7265625" style="17" customWidth="1"/>
     <x:col min="7" max="7" width="20.26953125" style="3" customWidth="1"/>
-    <x:col min="8" max="8" width="30.54296875" style="3" customWidth="1"/>
+    <x:col min="8" max="8" width="32.3671875" style="3" bestFit="1" customWidth="1"/>
     <x:col min="9" max="9" width="26.54296875" style="3" customWidth="1"/>
     <x:col min="10" max="16384" width="12.54296875" style="3"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:8" ht="15.75" customHeight="1">
+    <x:row r="1" spans="1:9" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B1" s="1"/>
       <x:c r="C1" s="1"/>
       <x:c r="D1" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E1" s="18"/>
       <x:c r="F1" s="18"/>
       <x:c r="G1" s="2"/>
       <x:c r="H1" s="2" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2" spans="1:9" ht="13.19999999999999928946">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="I1" s="3" t="s">
+        <x:v>50</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:9" ht="13.199999999999999">
       <x:c r="A2" s="1" t="s">
-        <x:v>6</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>5</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>5</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>5</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E2" s="18" t="s">
-        <x:v>3</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F2" s="18" t="s">
-        <x:v>5</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="G2" s="1" t="s">
-        <x:v>5</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="H2" s="1" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="I2" s="1"/>
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="I2" s="1" t="s">
+        <x:v>2</x:v>
+      </x:c>
     </x:row>
     <x:row r="3" spans="1:9" s="13" customFormat="1" ht="15.75" customHeight="1">
       <x:c r="A3" s="12" t="s">
-        <x:v>14</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B3" s="12" t="s">
         <x:v>18</x:v>
       </x:c>
       <x:c r="C3" s="12" t="s">
-        <x:v>7</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D3" s="12" t="s">
-        <x:v>11</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E3" s="19" t="s">
-        <x:v>20</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="F3" s="19" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="G3" s="14" t="s">
-        <x:v>12</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="H3" s="14" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="I3" s="15"/>
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="I3" s="15" t="s">
+        <x:v>49</x:v>
+      </x:c>
     </x:row>
     <x:row r="4" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A4" s="4" t="s">
-        <x:v>26</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B4" s="4" t="s">
-        <x:v>0</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C4" s="4" t="s">
-        <x:v>13</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D4" s="4" t="s">
-        <x:v>28</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E4" s="20" t="s">
-        <x:v>2</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="F4" s="20" t="s">
-        <x:v>10</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="G4" s="5"/>
       <x:c r="H4" s="5" t="s">
-        <x:v>32</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="I4" s="16"/>
       <x:c r="J4" s="5"/>
@@ -1092,23 +1152,23 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B5" s="6" t="s">
-        <x:v>25</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C5" s="6" t="s">
-        <x:v>24</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D5" s="6" t="s">
-        <x:v>4</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E5" s="21" t="s">
-        <x:v>1</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F5" s="21" t="s">
-        <x:v>9</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="G5" s="5"/>
       <x:c r="H5" s="5" t="s">
-        <x:v>31</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="I5" s="5"/>
       <x:c r="J5" s="5"/>
@@ -1123,26 +1183,26 @@
     </x:row>
     <x:row r="6" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A6" s="27" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="B6" s="27" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="B6" s="27" t="s">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="C6" s="4" t="s">
-        <x:v>23</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D6" s="4" t="s">
-        <x:v>29</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E6" s="20" t="s">
-        <x:v>2</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="F6" s="26" t="s">
-        <x:v>16</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="G6" s="5"/>
       <x:c r="H6" s="28" t="s">
-        <x:v>30</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="I6" s="5"/>
       <x:c r="J6" s="5"/>
@@ -1156,15 +1216,29 @@
       <x:c r="R6" s="5"/>
     </x:row>
     <x:row r="7" spans="1:18" ht="15.75" customHeight="1">
-      <x:c r="A7" s="7"/>
-      <x:c r="B7" s="7"/>
-      <x:c r="C7" s="7"/>
-      <x:c r="D7" s="7"/>
+      <x:c r="A7" s="6" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="B7" s="6" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C7" s="7" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D7" s="7" t="s">
+        <x:v>4</x:v>
+      </x:c>
       <x:c r="E7" s="22"/>
-      <x:c r="F7" s="22"/>
+      <x:c r="F7" s="22" t="s">
+        <x:v>45</x:v>
+      </x:c>
       <x:c r="G7" s="5"/>
-      <x:c r="H7" s="5"/>
-      <x:c r="I7" s="5"/>
+      <x:c r="H7" s="5" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="I7" s="5">
+        <x:v>10</x:v>
+      </x:c>
       <x:c r="J7" s="5"/>
       <x:c r="K7" s="5"/>
       <x:c r="L7" s="5"/>
@@ -1176,15 +1250,29 @@
       <x:c r="R7" s="5"/>
     </x:row>
     <x:row r="8" spans="1:18" ht="15.75" customHeight="1">
-      <x:c r="A8" s="7"/>
-      <x:c r="B8" s="7"/>
-      <x:c r="C8" s="7"/>
-      <x:c r="D8" s="7"/>
+      <x:c r="A8" s="6" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B8" s="6" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C8" s="7" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D8" s="7" t="s">
+        <x:v>48</x:v>
+      </x:c>
       <x:c r="E8" s="22"/>
-      <x:c r="F8" s="22"/>
+      <x:c r="F8" s="22" t="s">
+        <x:v>43</x:v>
+      </x:c>
       <x:c r="G8" s="5"/>
-      <x:c r="H8" s="5"/>
-      <x:c r="I8" s="5"/>
+      <x:c r="H8" s="5" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="I8" s="5">
+        <x:v>50</x:v>
+      </x:c>
       <x:c r="J8" s="5"/>
       <x:c r="K8" s="5"/>
       <x:c r="L8" s="5"/>
@@ -1196,15 +1284,29 @@
       <x:c r="R8" s="5"/>
     </x:row>
     <x:row r="9" spans="1:18" ht="15.75" customHeight="1">
-      <x:c r="A9" s="1"/>
-      <x:c r="B9" s="1"/>
-      <x:c r="C9" s="1"/>
-      <x:c r="D9" s="1"/>
+      <x:c r="A9" s="6" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="B9" s="6" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C9" s="1" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="D9" s="1" t="s">
+        <x:v>26</x:v>
+      </x:c>
       <x:c r="E9" s="18"/>
-      <x:c r="F9" s="18"/>
+      <x:c r="F9" s="18" t="s">
+        <x:v>5</x:v>
+      </x:c>
       <x:c r="G9" s="5"/>
-      <x:c r="H9" s="5"/>
-      <x:c r="I9" s="5"/>
+      <x:c r="H9" s="5" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I9" s="5">
+        <x:v>100</x:v>
+      </x:c>
       <x:c r="J9" s="5"/>
       <x:c r="K9" s="5"/>
       <x:c r="L9" s="5"/>
@@ -2447,7 +2549,7 @@
     <x:row r="998" ht="15.75" customHeight="1"/>
     <x:row r="999" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:pageMargins left="0.69972223043441772461" right="0.69972223043441772461" top="0.75" bottom="0.75" header="0.30000001192092895508" footer="0.30000001192092895508"/>
+  <x:pageMargins left="0.69972223043441772" right="0.69972223043441772" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>
   <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="1" fitToHeight="1" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="600" verticalDpi="600" copies="1"/>
 </x:worksheet>
 </file>
--- a/JsonConverter/ExcelFiles/DNFieldObject.xlsx
+++ b/JsonConverter/ExcelFiles/DNFieldObject.xlsx
@@ -19,159 +19,162 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="51">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="52">
+  <x:si>
+    <x:t>2DPrefab/DropItem_ManaBallOrange</x:t>
+  </x:si>
+  <x:si>
+    <x:t>몬스터 설명 (도감용)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DropItemDataId</x:t>
+  </x:si>
+  <x:si>
+    <x:t>우선 프리팹으로 구현하자!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Potato_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FieldObjectType</x:t>
+  </x:si>
+  <x:si>
+    <x:t>harv_potate_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DropCountRange</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dropItem_gold_1</x:t>
+  </x:si>
   <x:si>
     <x:t>2DPrefab/DropItem_ManaBallPink</x:t>
   </x:si>
   <x:si>
+    <x:t>2DPrefab/DropItem_ManaBallBlue</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Exp</x:t>
+  </x:si>
+  <x:si>
+    <x:t>필드 채집용 감자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IconPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 고유 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Corn_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ManaPoints</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DropItem</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PrefabPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Gold_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>필드 채집용 옥수수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>harv_corn_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>소량 경험치</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대량 경험치</x:t>
+  </x:si>
+  <x:si>
+    <x:t>드랍된 금화</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10,100</x:t>
+  </x:si>
+  <x:si>
+    <x:t>중량 경험치</x:t>
+  </x:si>
+  <x:si>
+    <x:t>주황경험치볼</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Harvest</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10,1000</x:t>
+  </x:si>
+  <x:si>
     <x:t>파랑경험치볼</x:t>
   </x:si>
   <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>int[]</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>분홍경험치볼</x:t>
+  </x:si>
+  <x:si>
+    <x:t>감자</x:t>
+  </x:si>
+  <x:si>
     <x:t>int</x:t>
   </x:si>
   <x:si>
+    <x:t>마나량</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>옥수수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>금화</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_ManaBallPink_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_ManaBallBlue_1</x:t>
+  </x:si>
+  <x:si>
     <x:t>dropItem_manaballorange_1</x:t>
   </x:si>
   <x:si>
-    <x:t>소량 경험치</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_ManaBallPink_1</x:t>
+    <x:t>dropItem_manaballpink_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2DPrefab/Harvest_Corn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_ManaBallOrange_1</x:t>
   </x:si>
   <x:si>
     <x:t>2DPrefab/Harvest_Potato</x:t>
   </x:si>
   <x:si>
-    <x:t>2DPrefab/Harvest_Corn</x:t>
+    <x:t>dropItem_manaballblue_1</x:t>
   </x:si>
   <x:si>
     <x:t>2DPrefab/DropItem_Gold</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>int[]</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10,1000</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10,100</x:t>
-  </x:si>
-  <x:si>
-    <x:t>드랍된 금화</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Harvest</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dropItem_gold_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FieldObjectType</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DropCountRange</x:t>
-  </x:si>
-  <x:si>
-    <x:t>우선 프리팹으로 구현하자!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DropItemDataId</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Potato_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>몬스터 설명 (도감용)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>harv_potate_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2DPrefab/DropItem_ManaBallBlue</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대량 경험치</x:t>
-  </x:si>
-  <x:si>
-    <x:t>주황경험치볼</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 고유 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Corn_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Gold_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IconPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DropItem</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PrefabPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>필드 채집용 감자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>필드 채집용 옥수수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>harv_corn_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>금화</x:t>
-  </x:si>
-  <x:si>
-    <x:t>감자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>옥수수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dropItem_manaballblue_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_ManaBallOrange_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dropItem_manaballpink_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_ManaBallBlue_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2DPrefab/DropItem_ManaBallOrange</x:t>
-  </x:si>
-  <x:si>
-    <x:t>분홍경험치볼</x:t>
-  </x:si>
-  <x:si>
-    <x:t>중량 경험치</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ManaPoints</x:t>
-  </x:si>
-  <x:si>
-    <x:t>마나량</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1038,103 +1041,103 @@
   <x:sheetData>
     <x:row r="1" spans="1:9" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B1" s="1"/>
       <x:c r="C1" s="1"/>
       <x:c r="D1" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E1" s="18"/>
       <x:c r="F1" s="18"/>
       <x:c r="G1" s="2"/>
       <x:c r="H1" s="2" t="s">
-        <x:v>20</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="I1" s="3" t="s">
-        <x:v>50</x:v>
+        <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:9" ht="13.199999999999999">
       <x:c r="A2" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E2" s="18" t="s">
-        <x:v>10</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="F2" s="18" t="s">
-        <x:v>9</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="G2" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="H2" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="I2" s="1" t="s">
-        <x:v>2</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:9" s="13" customFormat="1" ht="15.75" customHeight="1">
       <x:c r="A3" s="12" t="s">
-        <x:v>38</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B3" s="12" t="s">
-        <x:v>18</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C3" s="12" t="s">
-        <x:v>16</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D3" s="12" t="s">
-        <x:v>31</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E3" s="19" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="F3" s="19" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G3" s="14" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="H3" s="14" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="F3" s="19" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="G3" s="14" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="H3" s="14" t="s">
-        <x:v>34</x:v>
-      </x:c>
       <x:c r="I3" s="15" t="s">
-        <x:v>49</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A4" s="4" t="s">
-        <x:v>37</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B4" s="4" t="s">
-        <x:v>15</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C4" s="4" t="s">
         <x:v>41</x:v>
       </x:c>
       <x:c r="D4" s="4" t="s">
-        <x:v>36</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E4" s="20" t="s">
-        <x:v>12</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="F4" s="20" t="s">
-        <x:v>29</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G4" s="5"/>
       <x:c r="H4" s="5" t="s">
-        <x:v>7</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="I4" s="16"/>
       <x:c r="J4" s="5"/>
@@ -1149,26 +1152,26 @@
     </x:row>
     <x:row r="5" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A5" s="6" t="s">
-        <x:v>17</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B5" s="6" t="s">
-        <x:v>33</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C5" s="6" t="s">
-        <x:v>39</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="D5" s="6" t="s">
-        <x:v>13</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E5" s="21" t="s">
-        <x:v>11</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="F5" s="21" t="s">
-        <x:v>30</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G5" s="5"/>
       <x:c r="H5" s="5" t="s">
-        <x:v>8</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="I5" s="5"/>
       <x:c r="J5" s="5"/>
@@ -1183,26 +1186,26 @@
     </x:row>
     <x:row r="6" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A6" s="27" t="s">
-        <x:v>24</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="B6" s="27" t="s">
-        <x:v>15</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C6" s="4" t="s">
-        <x:v>40</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D6" s="4" t="s">
-        <x:v>35</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E6" s="20" t="s">
-        <x:v>12</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="F6" s="26" t="s">
-        <x:v>22</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="G6" s="5"/>
       <x:c r="H6" s="28" t="s">
-        <x:v>6</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="I6" s="5"/>
       <x:c r="J6" s="5"/>
@@ -1217,24 +1220,24 @@
     </x:row>
     <x:row r="7" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A7" s="6" t="s">
-        <x:v>42</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B7" s="6" t="s">
-        <x:v>33</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C7" s="7" t="s">
-        <x:v>1</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D7" s="7" t="s">
-        <x:v>4</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E7" s="22"/>
       <x:c r="F7" s="22" t="s">
-        <x:v>45</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="G7" s="5"/>
       <x:c r="H7" s="5" t="s">
-        <x:v>25</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="I7" s="5">
         <x:v>10</x:v>
@@ -1251,24 +1254,24 @@
     </x:row>
     <x:row r="8" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A8" s="6" t="s">
-        <x:v>3</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B8" s="6" t="s">
-        <x:v>33</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C8" s="7" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="D8" s="7" t="s">
         <x:v>27</x:v>
-      </x:c>
-      <x:c r="D8" s="7" t="s">
-        <x:v>48</x:v>
       </x:c>
       <x:c r="E8" s="22"/>
       <x:c r="F8" s="22" t="s">
-        <x:v>43</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="G8" s="5"/>
       <x:c r="H8" s="5" t="s">
-        <x:v>46</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I8" s="5">
         <x:v>50</x:v>
@@ -1285,24 +1288,24 @@
     </x:row>
     <x:row r="9" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A9" s="6" t="s">
-        <x:v>44</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B9" s="6" t="s">
-        <x:v>33</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E9" s="18"/>
       <x:c r="F9" s="18" t="s">
-        <x:v>5</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="G9" s="5"/>
       <x:c r="H9" s="5" t="s">
-        <x:v>0</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="I9" s="5">
         <x:v>100</x:v>

--- a/JsonConverter/ExcelFiles/DNFieldObject.xlsx
+++ b/JsonConverter/ExcelFiles/DNFieldObject.xlsx
@@ -19,162 +19,237 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="52">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="77">
+  <x:si>
+    <x:t>dropItem_wand_dmgup_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Gold_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>몬스터 설명 (도감용)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>harv_potate_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DropCountRange</x:t>
+  </x:si>
+  <x:si>
+    <x:t>우선 프리팹으로 구현하자!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dropItem_gold_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Potato_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FieldObjectType</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DropItemDataId</x:t>
+  </x:si>
+  <x:si>
+    <x:t>금화</x:t>
+  </x:si>
+  <x:si>
+    <x:t>옥수수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Exp</x:t>
+  </x:si>
+  <x:si>
+    <x:t>감자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>마나량</x:t>
+  </x:si>
+  <x:si>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dropItem_chest_1</x:t>
+  </x:si>
   <x:si>
     <x:t>2DPrefab/DropItem_ManaBallOrange</x:t>
   </x:si>
   <x:si>
-    <x:t>몬스터 설명 (도감용)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DropItemDataId</x:t>
-  </x:si>
-  <x:si>
-    <x:t>우선 프리팹으로 구현하자!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Potato_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FieldObjectType</x:t>
-  </x:si>
-  <x:si>
-    <x:t>harv_potate_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DropCountRange</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dropItem_gold_1</x:t>
+    <x:t>Harvest</x:t>
+  </x:si>
+  <x:si>
+    <x:t>드랍된 금화</x:t>
+  </x:si>
+  <x:si>
+    <x:t>중량 경험치</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10,100</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대량 경험치</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10,1000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>주황경험치볼</x:t>
+  </x:si>
+  <x:si>
+    <x:t>파랑경험치볼</x:t>
+  </x:si>
+  <x:si>
+    <x:t>int[]</x:t>
+  </x:si>
+  <x:si>
+    <x:t>소량 경험치</x:t>
+  </x:si>
+  <x:si>
+    <x:t>분홍경험치볼</x:t>
+  </x:si>
+  <x:si>
+    <x:t>필드 채집용 감자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2DPrefab/DropItem_ManaBallBlue</x:t>
   </x:si>
   <x:si>
     <x:t>2DPrefab/DropItem_ManaBallPink</x:t>
   </x:si>
   <x:si>
-    <x:t>2DPrefab/DropItem_ManaBallBlue</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Exp</x:t>
-  </x:si>
-  <x:si>
-    <x:t>필드 채집용 감자</x:t>
+    <x:t>2DPrefab/DropItem_WandDmgUp</x:t>
   </x:si>
   <x:si>
     <x:t>Description</x:t>
   </x:si>
   <x:si>
+    <x:t>Item_Gold_1</x:t>
+  </x:si>
+  <x:si>
     <x:t>IconPath</x:t>
   </x:si>
   <x:si>
+    <x:t>Item_Corn_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DropItem</x:t>
+  </x:si>
+  <x:si>
     <x:t>캐릭터 고유 ID</x:t>
   </x:si>
   <x:si>
-    <x:t>Item_Corn_1</x:t>
+    <x:t>harv_corn_1</x:t>
   </x:si>
   <x:si>
     <x:t>ManaPoints</x:t>
   </x:si>
   <x:si>
-    <x:t>DropItem</x:t>
-  </x:si>
-  <x:si>
     <x:t>PrefabPath</x:t>
   </x:si>
   <x:si>
-    <x:t>Item_Gold_1</x:t>
-  </x:si>
-  <x:si>
     <x:t>필드 채집용 옥수수</x:t>
   </x:si>
   <x:si>
-    <x:t>harv_corn_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>소량 경험치</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대량 경험치</x:t>
-  </x:si>
-  <x:si>
-    <x:t>드랍된 금화</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10,100</x:t>
-  </x:si>
-  <x:si>
-    <x:t>중량 경험치</x:t>
-  </x:si>
-  <x:si>
-    <x:t>주황경험치볼</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Harvest</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10,1000</x:t>
-  </x:si>
-  <x:si>
-    <x:t>파랑경험치볼</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>int[]</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>분홍경험치볼</x:t>
-  </x:si>
-  <x:si>
-    <x:t>감자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>int</x:t>
-  </x:si>
-  <x:si>
-    <x:t>마나량</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>옥수수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>금화</x:t>
+    <x:t>Item_ManaBallBlue_1</x:t>
   </x:si>
   <x:si>
     <x:t>Item_ManaBallPink_1</x:t>
   </x:si>
   <x:si>
-    <x:t>Item_ManaBallBlue_1</x:t>
+    <x:t>Item_ManaBallOrange_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2DPrefab/Harvest_Potato</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2DPrefab/DropItem_Gold</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2DPrefab/Harvest_Corn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dropItem_manaballblue_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dropItem_manaballpink_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2DPrefab/DropItem_Heart</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2DPrefab/DropItem_Wand</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Wand_DmgUp_1</x:t>
   </x:si>
   <x:si>
     <x:t>dropItem_manaballorange_1</x:t>
   </x:si>
   <x:si>
-    <x:t>dropItem_manaballpink_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2DPrefab/Harvest_Corn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_ManaBallOrange_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2DPrefab/Harvest_Potato</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dropItem_manaballblue_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2DPrefab/DropItem_Gold</x:t>
+    <x:t>랜덤한 이벤트가 발생한다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>공격력과 이동속도가 대폭 증가한다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dropItem_heart_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Heart_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>하트</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Chest_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dropItem_wand_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Chest_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Wand_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>상자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2DPrefab/DropItem_Chest</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Wand_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>체력을 회복한다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>지팡이</x:t>
+  </x:si>
+  <x:si>
+    <x:t>공격력과 이동속도가 소량 증가한다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>고급지팡이</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Heart_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Wand_DmgUp_1</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1033,7 +1108,7 @@
     <x:col min="3" max="3" width="19.54296875" style="3" customWidth="1"/>
     <x:col min="4" max="4" width="50.7265625" style="3" customWidth="1"/>
     <x:col min="5" max="6" width="50.7265625" style="17" customWidth="1"/>
-    <x:col min="7" max="7" width="20.26953125" style="3" customWidth="1"/>
+    <x:col min="7" max="7" width="24.14453125" style="3" bestFit="1" customWidth="1"/>
     <x:col min="8" max="8" width="32.3671875" style="3" bestFit="1" customWidth="1"/>
     <x:col min="9" max="9" width="26.54296875" style="3" customWidth="1"/>
     <x:col min="10" max="16384" width="12.54296875" style="3"/>
@@ -1041,103 +1116,103 @@
   <x:sheetData>
     <x:row r="1" spans="1:9" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B1" s="1"/>
       <x:c r="C1" s="1"/>
       <x:c r="D1" s="1" t="s">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="E1" s="18"/>
       <x:c r="F1" s="18"/>
       <x:c r="G1" s="2"/>
       <x:c r="H1" s="2" t="s">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="I1" s="3" t="s">
-        <x:v>39</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:9" ht="13.199999999999999">
       <x:c r="A2" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="E2" s="18" t="s">
-        <x:v>34</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F2" s="18" t="s">
-        <x:v>29</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="G2" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="H2" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="I2" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:9" s="13" customFormat="1" ht="15.75" customHeight="1">
       <x:c r="A3" s="12" t="s">
-        <x:v>40</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B3" s="12" t="s">
-        <x:v>5</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C3" s="12" t="s">
-        <x:v>35</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D3" s="12" t="s">
-        <x:v>13</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E3" s="19" t="s">
-        <x:v>7</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F3" s="19" t="s">
-        <x:v>2</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="G3" s="14" t="s">
-        <x:v>14</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="H3" s="14" t="s">
-        <x:v>19</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="I3" s="15" t="s">
-        <x:v>17</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A4" s="4" t="s">
-        <x:v>22</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B4" s="4" t="s">
-        <x:v>30</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C4" s="4" t="s">
-        <x:v>41</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D4" s="4" t="s">
-        <x:v>21</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E4" s="20" t="s">
-        <x:v>26</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F4" s="20" t="s">
-        <x:v>16</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G4" s="5"/>
       <x:c r="H4" s="5" t="s">
-        <x:v>47</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="I4" s="16"/>
       <x:c r="J4" s="5"/>
@@ -1152,24 +1227,26 @@
     </x:row>
     <x:row r="5" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A5" s="6" t="s">
-        <x:v>8</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="B5" s="6" t="s">
-        <x:v>18</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C5" s="6" t="s">
-        <x:v>42</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D5" s="6" t="s">
-        <x:v>25</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="E5" s="21" t="s">
-        <x:v>31</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F5" s="21" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="G5" s="5"/>
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="G5" s="5" t="s">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="H5" s="5" t="s">
         <x:v>51</x:v>
       </x:c>
@@ -1186,26 +1263,26 @@
     </x:row>
     <x:row r="6" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A6" s="27" t="s">
-        <x:v>6</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B6" s="27" t="s">
-        <x:v>30</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C6" s="4" t="s">
-        <x:v>37</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D6" s="4" t="s">
-        <x:v>12</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E6" s="20" t="s">
-        <x:v>26</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F6" s="26" t="s">
-        <x:v>4</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="G6" s="5"/>
       <x:c r="H6" s="28" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="I6" s="5"/>
       <x:c r="J6" s="5"/>
@@ -1220,24 +1297,24 @@
     </x:row>
     <x:row r="7" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A7" s="6" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B7" s="6" t="s">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C7" s="7" t="s">
-        <x:v>32</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D7" s="7" t="s">
-        <x:v>23</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E7" s="22"/>
       <x:c r="F7" s="22" t="s">
-        <x:v>44</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="G7" s="5"/>
       <x:c r="H7" s="5" t="s">
-        <x:v>10</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="I7" s="5">
         <x:v>10</x:v>
@@ -1254,24 +1331,24 @@
     </x:row>
     <x:row r="8" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A8" s="6" t="s">
-        <x:v>45</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B8" s="6" t="s">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C8" s="7" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="D8" s="7" t="s">
-        <x:v>27</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E8" s="22"/>
       <x:c r="F8" s="22" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="G8" s="5"/>
       <x:c r="H8" s="5" t="s">
-        <x:v>0</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="I8" s="5">
         <x:v>50</x:v>
@@ -1288,24 +1365,24 @@
     </x:row>
     <x:row r="9" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A9" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B9" s="6" t="s">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E9" s="18"/>
       <x:c r="F9" s="18" t="s">
-        <x:v>43</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="G9" s="5"/>
       <x:c r="H9" s="5" t="s">
-        <x:v>9</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="I9" s="5">
         <x:v>100</x:v>
@@ -1321,14 +1398,28 @@
       <x:c r="R9" s="5"/>
     </x:row>
     <x:row r="10" spans="1:18" ht="15.75" customHeight="1">
-      <x:c r="A10" s="1"/>
-      <x:c r="B10" s="1"/>
-      <x:c r="C10" s="1"/>
-      <x:c r="D10" s="1"/>
+      <x:c r="A10" s="1" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="B10" s="6" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="C10" s="1" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="D10" s="1" t="s">
+        <x:v>71</x:v>
+      </x:c>
       <x:c r="E10" s="18"/>
-      <x:c r="F10" s="18"/>
-      <x:c r="G10" s="5"/>
-      <x:c r="H10" s="5"/>
+      <x:c r="F10" s="18" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="G10" s="5" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="H10" s="5" t="s">
+        <x:v>55</x:v>
+      </x:c>
       <x:c r="I10" s="5"/>
       <x:c r="J10" s="5"/>
       <x:c r="K10" s="5"/>
@@ -1341,14 +1432,28 @@
       <x:c r="R10" s="5"/>
     </x:row>
     <x:row r="11" spans="1:18" ht="15.75" customHeight="1">
-      <x:c r="A11" s="7"/>
-      <x:c r="B11" s="7"/>
-      <x:c r="C11" s="7"/>
-      <x:c r="D11" s="7"/>
+      <x:c r="A11" s="7" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="B11" s="6" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="C11" s="7" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="D11" s="7" t="s">
+        <x:v>73</x:v>
+      </x:c>
       <x:c r="E11" s="22"/>
-      <x:c r="F11" s="22"/>
-      <x:c r="G11" s="5"/>
-      <x:c r="H11" s="5"/>
+      <x:c r="F11" s="22" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="G11" s="5" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="H11" s="5" t="s">
+        <x:v>56</x:v>
+      </x:c>
       <x:c r="I11" s="5"/>
       <x:c r="J11" s="5"/>
       <x:c r="K11" s="5"/>
@@ -1361,14 +1466,28 @@
       <x:c r="R11" s="5"/>
     </x:row>
     <x:row r="12" spans="1:18" ht="15.75" customHeight="1">
-      <x:c r="A12" s="4"/>
-      <x:c r="B12" s="4"/>
-      <x:c r="C12" s="4"/>
-      <x:c r="D12" s="4"/>
+      <x:c r="A12" s="4" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B12" s="6" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="C12" s="4" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="D12" s="4" t="s">
+        <x:v>59</x:v>
+      </x:c>
       <x:c r="E12" s="20"/>
-      <x:c r="F12" s="20"/>
-      <x:c r="G12" s="5"/>
-      <x:c r="H12" s="5"/>
+      <x:c r="F12" s="20" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="G12" s="5" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="H12" s="5" t="s">
+        <x:v>69</x:v>
+      </x:c>
       <x:c r="I12" s="5"/>
       <x:c r="J12" s="5"/>
       <x:c r="K12" s="5"/>
@@ -1381,14 +1500,28 @@
       <x:c r="R12" s="5"/>
     </x:row>
     <x:row r="13" spans="1:18" ht="15.75" customHeight="1">
-      <x:c r="A13" s="1"/>
-      <x:c r="B13" s="1"/>
-      <x:c r="C13" s="1"/>
-      <x:c r="D13" s="1"/>
+      <x:c r="A13" s="1" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="B13" s="6" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="C13" s="1" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="D13" s="1" t="s">
+        <x:v>60</x:v>
+      </x:c>
       <x:c r="E13" s="18"/>
-      <x:c r="F13" s="18"/>
-      <x:c r="G13" s="5"/>
-      <x:c r="H13" s="5"/>
+      <x:c r="F13" s="18" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="G13" s="5" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="H13" s="5" t="s">
+        <x:v>36</x:v>
+      </x:c>
       <x:c r="I13" s="5"/>
       <x:c r="J13" s="5"/>
       <x:c r="K13" s="5"/>

--- a/JsonConverter/ExcelFiles/DNFieldObject.xlsx
+++ b/JsonConverter/ExcelFiles/DNFieldObject.xlsx
@@ -19,237 +19,258 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="77">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="84">
+  <x:si>
+    <x:t>SpeedAmount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>float</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2DPrefab/DropItem_ManaBallOrange</x:t>
+  </x:si>
+  <x:si>
+    <x:t>힐량</x:t>
+  </x:si>
+  <x:si>
+    <x:t>필드 채집용 감자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 고유 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IconPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Gold_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Corn_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>harv_corn_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PrefabPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DropItem</x:t>
+  </x:si>
+  <x:si>
+    <x:t>필드 채집용 옥수수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ManaPoints</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Wand_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>체력을 회복한다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2DPrefab/DropItem_ManaBallBlue</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2DPrefab/DropItem_ManaBallPink</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Harvest</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10,1000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>드랍된 금화</x:t>
+  </x:si>
+  <x:si>
+    <x:t>파랑경험치볼</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>주황경험치볼</x:t>
+  </x:si>
+  <x:si>
+    <x:t>고급지팡이</x:t>
+  </x:si>
+  <x:si>
+    <x:t>소량 경험치</x:t>
+  </x:si>
+  <x:si>
+    <x:t>분홍경험치볼</x:t>
+  </x:si>
+  <x:si>
+    <x:t>중량 경험치</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10,100</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대량 경험치</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>int[]</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Exp</x:t>
+  </x:si>
+  <x:si>
+    <x:t>감자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>금화</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>하트</x:t>
+  </x:si>
+  <x:si>
+    <x:t>상자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>옥수수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>지팡이</x:t>
+  </x:si>
+  <x:si>
+    <x:t>마나량</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Wand_DmgUp_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>공격력과 이동속도가 대폭 증가한다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Wand_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_ManaBallPink_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dropItem_chest_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_ManaBallBlue_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>공격력과 이동속도가 소량 증가한다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dropItem_heart_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Chest_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Gold_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Heart_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dropItem_manaballorange_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2DPrefab/DropItem_WandDmgUp</x:t>
+  </x:si>
   <x:si>
     <x:t>dropItem_wand_dmgup_1</x:t>
   </x:si>
   <x:si>
-    <x:t>Icon/Icon_Gold_1</x:t>
+    <x:t>2DPrefab/DropItem_Gold</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_ManaBallOrange_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2DPrefab/Harvest_Corn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dropItem_manaballblue_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2DPrefab/DropItem_Heart</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Wand_DmgUp_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2DPrefab/DropItem_Wand</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2DPrefab/Harvest_Potato</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dropItem_manaballpink_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2DPrefab/DropItem_Chest</x:t>
+  </x:si>
+  <x:si>
+    <x:t>harv_potate_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Heart_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>우선 프리팹으로 구현하자!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Chest_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Potato_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dropItem_wand_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DropItemDataId</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FieldObjectType</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dropItem_gold_1</x:t>
   </x:si>
   <x:si>
     <x:t>몬스터 설명 (도감용)</x:t>
   </x:si>
   <x:si>
-    <x:t>harv_potate_1</x:t>
+    <x:t>랜덤한 이벤트가 발생한다</x:t>
   </x:si>
   <x:si>
     <x:t>DropCountRange</x:t>
   </x:si>
   <x:si>
-    <x:t>우선 프리팹으로 구현하자!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dropItem_gold_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Potato_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FieldObjectType</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DropItemDataId</x:t>
-  </x:si>
-  <x:si>
-    <x:t>금화</x:t>
-  </x:si>
-  <x:si>
-    <x:t>옥수수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Exp</x:t>
-  </x:si>
-  <x:si>
-    <x:t>감자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>마나량</x:t>
-  </x:si>
-  <x:si>
-    <x:t>int</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dropItem_chest_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2DPrefab/DropItem_ManaBallOrange</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Harvest</x:t>
-  </x:si>
-  <x:si>
-    <x:t>드랍된 금화</x:t>
-  </x:si>
-  <x:si>
-    <x:t>중량 경험치</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10,100</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대량 경험치</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10,1000</x:t>
-  </x:si>
-  <x:si>
-    <x:t>주황경험치볼</x:t>
-  </x:si>
-  <x:si>
-    <x:t>파랑경험치볼</x:t>
-  </x:si>
-  <x:si>
-    <x:t>int[]</x:t>
-  </x:si>
-  <x:si>
-    <x:t>소량 경험치</x:t>
-  </x:si>
-  <x:si>
-    <x:t>분홍경험치볼</x:t>
-  </x:si>
-  <x:si>
-    <x:t>필드 채집용 감자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2DPrefab/DropItem_ManaBallBlue</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2DPrefab/DropItem_ManaBallPink</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2DPrefab/DropItem_WandDmgUp</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Gold_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IconPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Corn_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DropItem</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 고유 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>harv_corn_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ManaPoints</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PrefabPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>필드 채집용 옥수수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_ManaBallBlue_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_ManaBallPink_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_ManaBallOrange_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2DPrefab/Harvest_Potato</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2DPrefab/DropItem_Gold</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2DPrefab/Harvest_Corn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dropItem_manaballblue_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dropItem_manaballpink_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2DPrefab/DropItem_Heart</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2DPrefab/DropItem_Wand</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Wand_DmgUp_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dropItem_manaballorange_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>랜덤한 이벤트가 발생한다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>공격력과 이동속도가 대폭 증가한다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dropItem_heart_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Heart_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>하트</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Chest_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dropItem_wand_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Chest_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Wand_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>상자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2DPrefab/DropItem_Chest</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Wand_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>체력을 회복한다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>지팡이</x:t>
-  </x:si>
-  <x:si>
-    <x:t>공격력과 이동속도가 소량 증가한다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>고급지팡이</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Heart_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Wand_DmgUp_1</x:t>
+    <x:t>데미지증가량</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이속증가량</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HealAmount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DmgAmount</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1111,108 +1132,136 @@
     <x:col min="7" max="7" width="24.14453125" style="3" bestFit="1" customWidth="1"/>
     <x:col min="8" max="8" width="32.3671875" style="3" bestFit="1" customWidth="1"/>
     <x:col min="9" max="9" width="26.54296875" style="3" customWidth="1"/>
-    <x:col min="10" max="16384" width="12.54296875" style="3"/>
+    <x:col min="10" max="12" width="12.54296875" style="3" bestFit="1" customWidth="1"/>
+    <x:col min="13" max="16384" width="12.54296875" style="3"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:9" ht="15.75" customHeight="1">
+    <x:row r="1" spans="1:12" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="B1" s="1"/>
       <x:c r="C1" s="1"/>
       <x:c r="D1" s="1" t="s">
-        <x:v>2</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="E1" s="18"/>
       <x:c r="F1" s="18"/>
       <x:c r="G1" s="2"/>
       <x:c r="H1" s="2" t="s">
-        <x:v>5</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="I1" s="3" t="s">
-        <x:v>14</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2" spans="1:9" ht="13.199999999999999">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="J1" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K1" s="3" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="L1" s="3" t="s">
+        <x:v>81</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:12" ht="13.199999999999999">
       <x:c r="A2" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E2" s="18" t="s">
-        <x:v>30</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="F2" s="18" t="s">
-        <x:v>22</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="G2" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="H2" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="I2" s="1" t="s">
-        <x:v>15</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" spans="1:9" s="13" customFormat="1" ht="15.75" customHeight="1">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="J2" s="3" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="K2" s="3" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L2" s="3" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:12" s="13" customFormat="1" ht="15.75" customHeight="1">
       <x:c r="A3" s="12" t="s">
-        <x:v>16</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B3" s="12" t="s">
-        <x:v>8</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C3" s="12" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="D3" s="12" t="s">
-        <x:v>37</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E3" s="19" t="s">
-        <x:v>4</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="F3" s="19" t="s">
-        <x:v>9</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="G3" s="14" t="s">
-        <x:v>39</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="H3" s="14" t="s">
-        <x:v>45</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="I3" s="15" t="s">
-        <x:v>44</x:v>
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="J3" s="13" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="K3" s="13" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="L3" s="13" t="s">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A4" s="4" t="s">
-        <x:v>43</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B4" s="4" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="C4" s="4" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D4" s="4" t="s">
-        <x:v>46</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E4" s="20" t="s">
-        <x:v>24</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F4" s="20" t="s">
-        <x:v>40</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="G4" s="5"/>
       <x:c r="H4" s="5" t="s">
-        <x:v>52</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="I4" s="16"/>
       <x:c r="J4" s="5"/>
@@ -1227,28 +1276,28 @@
     </x:row>
     <x:row r="5" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A5" s="6" t="s">
-        <x:v>6</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B5" s="6" t="s">
-        <x:v>41</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C5" s="6" t="s">
-        <x:v>10</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D5" s="6" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="E5" s="21" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="E5" s="21" t="s">
-        <x:v>27</x:v>
-      </x:c>
       <x:c r="F5" s="21" t="s">
-        <x:v>38</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="G5" s="5" t="s">
-        <x:v>1</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="H5" s="5" t="s">
-        <x:v>51</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="I5" s="5"/>
       <x:c r="J5" s="5"/>
@@ -1263,26 +1312,26 @@
     </x:row>
     <x:row r="6" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A6" s="27" t="s">
-        <x:v>3</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B6" s="27" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="C6" s="4" t="s">
-        <x:v>13</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D6" s="4" t="s">
-        <x:v>33</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E6" s="20" t="s">
-        <x:v>24</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F6" s="26" t="s">
-        <x:v>7</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="G6" s="5"/>
       <x:c r="H6" s="28" t="s">
-        <x:v>50</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="I6" s="5"/>
       <x:c r="J6" s="5"/>
@@ -1297,24 +1346,24 @@
     </x:row>
     <x:row r="7" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A7" s="6" t="s">
-        <x:v>53</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B7" s="6" t="s">
-        <x:v>12</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C7" s="7" t="s">
-        <x:v>29</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D7" s="7" t="s">
-        <x:v>31</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E7" s="22"/>
       <x:c r="F7" s="22" t="s">
-        <x:v>47</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="G7" s="5"/>
       <x:c r="H7" s="5" t="s">
-        <x:v>34</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="I7" s="5">
         <x:v>10</x:v>
@@ -1331,24 +1380,24 @@
     </x:row>
     <x:row r="8" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A8" s="6" t="s">
-        <x:v>58</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B8" s="6" t="s">
-        <x:v>12</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C8" s="7" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="D8" s="7" t="s">
         <x:v>28</x:v>
-      </x:c>
-      <x:c r="D8" s="7" t="s">
-        <x:v>21</x:v>
       </x:c>
       <x:c r="E8" s="22"/>
       <x:c r="F8" s="22" t="s">
-        <x:v>49</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="G8" s="5"/>
       <x:c r="H8" s="5" t="s">
-        <x:v>18</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="I8" s="5">
         <x:v>50</x:v>
@@ -1365,24 +1414,24 @@
     </x:row>
     <x:row r="9" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A9" s="6" t="s">
-        <x:v>54</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B9" s="6" t="s">
-        <x:v>12</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E9" s="18"/>
       <x:c r="F9" s="18" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="G9" s="5"/>
       <x:c r="H9" s="5" t="s">
-        <x:v>35</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="I9" s="5">
         <x:v>100</x:v>
@@ -1399,29 +1448,31 @@
     </x:row>
     <x:row r="10" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A10" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B10" s="6" t="s">
-        <x:v>41</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E10" s="18"/>
       <x:c r="F10" s="18" t="s">
-        <x:v>75</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="G10" s="5" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="H10" s="5" t="s">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="H10" s="5" t="s">
-        <x:v>55</x:v>
-      </x:c>
       <x:c r="I10" s="5"/>
-      <x:c r="J10" s="5"/>
+      <x:c r="J10" s="5">
+        <x:v>300</x:v>
+      </x:c>
       <x:c r="K10" s="5"/>
       <x:c r="L10" s="5"/>
       <x:c r="M10" s="5"/>
@@ -1433,31 +1484,35 @@
     </x:row>
     <x:row r="11" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A11" s="7" t="s">
-        <x:v>65</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B11" s="6" t="s">
-        <x:v>41</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C11" s="7" t="s">
-        <x:v>72</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="D11" s="7" t="s">
-        <x:v>73</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E11" s="22"/>
       <x:c r="F11" s="22" t="s">
-        <x:v>70</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G11" s="5" t="s">
-        <x:v>67</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="H11" s="5" t="s">
-        <x:v>56</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="I11" s="5"/>
       <x:c r="J11" s="5"/>
-      <x:c r="K11" s="5"/>
-      <x:c r="L11" s="5"/>
+      <x:c r="K11" s="5">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="L11" s="5">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="M11" s="5"/>
       <x:c r="N11" s="5"/>
       <x:c r="O11" s="5"/>
@@ -1467,26 +1522,26 @@
     </x:row>
     <x:row r="12" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A12" s="4" t="s">
-        <x:v>17</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B12" s="6" t="s">
-        <x:v>41</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C12" s="4" t="s">
-        <x:v>68</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D12" s="4" t="s">
-        <x:v>59</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="E12" s="20"/>
       <x:c r="F12" s="20" t="s">
-        <x:v>66</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="G12" s="5" t="s">
-        <x:v>64</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="H12" s="5" t="s">
-        <x:v>69</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="I12" s="5"/>
       <x:c r="J12" s="5"/>
@@ -1501,31 +1556,35 @@
     </x:row>
     <x:row r="13" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A13" s="1" t="s">
-        <x:v>0</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B13" s="6" t="s">
-        <x:v>41</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E13" s="18"/>
       <x:c r="F13" s="18" t="s">
-        <x:v>76</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="G13" s="5" t="s">
-        <x:v>57</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="H13" s="5" t="s">
-        <x:v>36</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="I13" s="5"/>
       <x:c r="J13" s="5"/>
-      <x:c r="K13" s="5"/>
-      <x:c r="L13" s="5"/>
+      <x:c r="K13" s="5">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="L13" s="5">
+        <x:v>3</x:v>
+      </x:c>
       <x:c r="M13" s="5"/>
       <x:c r="N13" s="5"/>
       <x:c r="O13" s="5"/>

--- a/JsonConverter/ExcelFiles/DNFieldObject.xlsx
+++ b/JsonConverter/ExcelFiles/DNFieldObject.xlsx
@@ -21,256 +21,256 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="84">
   <x:si>
+    <x:t>2DPrefab/DropItem_ManaBallOrange</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HealAmount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DmgAmount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>분홍경험치볼</x:t>
+  </x:si>
+  <x:si>
+    <x:t>드랍된 금화</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10,100</x:t>
+  </x:si>
+  <x:si>
+    <x:t>고급지팡이</x:t>
+  </x:si>
+  <x:si>
+    <x:t>소량 경험치</x:t>
+  </x:si>
+  <x:si>
+    <x:t>중량 경험치</x:t>
+  </x:si>
+  <x:si>
+    <x:t>float</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10,1000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Harvest</x:t>
+  </x:si>
+  <x:si>
+    <x:t>주황경험치볼</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>파랑경험치볼</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대량 경험치</x:t>
+  </x:si>
+  <x:si>
+    <x:t>int[]</x:t>
+  </x:si>
+  <x:si>
+    <x:t>데미지증가량</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이속증가량</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dropItem_wand_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Heart_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>harv_potate_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FieldObjectType</x:t>
+  </x:si>
+  <x:si>
+    <x:t>몬스터 설명 (도감용)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>랜덤한 이벤트가 발생한다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DropCountRange</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DropItemDataId</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dropItem_gold_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>우선 프리팹으로 구현하자!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Chest_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Potato_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2DPrefab/DropItem_ManaBallPink</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2DPrefab/DropItem_ManaBallBlue</x:t>
+  </x:si>
+  <x:si>
+    <x:t>금화</x:t>
+  </x:si>
+  <x:si>
+    <x:t>감자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>하트</x:t>
+  </x:si>
+  <x:si>
+    <x:t>마나량</x:t>
+  </x:si>
+  <x:si>
+    <x:t>지팡이</x:t>
+  </x:si>
+  <x:si>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>상자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>옥수수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Exp</x:t>
+  </x:si>
+  <x:si>
+    <x:t>힐량</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dropItem_heart_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dropItem_chest_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Wand_DmgUp_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_ManaBallPink_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>공격력과 이동속도가 대폭 증가한다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Wand_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_ManaBallBlue_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>공격력과 이동속도가 소량 증가한다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Gold_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Chest_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Heart_1</x:t>
+  </x:si>
+  <x:si>
     <x:t>SpeedAmount</x:t>
   </x:si>
   <x:si>
-    <x:t>float</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2DPrefab/DropItem_ManaBallOrange</x:t>
-  </x:si>
-  <x:si>
-    <x:t>힐량</x:t>
+    <x:t>캐릭터 고유 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Corn_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>harv_corn_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IconPath</x:t>
   </x:si>
   <x:si>
     <x:t>필드 채집용 감자</x:t>
   </x:si>
   <x:si>
-    <x:t>캐릭터 고유 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IconPath</x:t>
-  </x:si>
-  <x:si>
     <x:t>Item_Gold_1</x:t>
   </x:si>
   <x:si>
-    <x:t>Item_Corn_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>harv_corn_1</x:t>
+    <x:t>ManaPoints</x:t>
+  </x:si>
+  <x:si>
+    <x:t>체력을 회복한다</x:t>
   </x:si>
   <x:si>
     <x:t>PrefabPath</x:t>
   </x:si>
   <x:si>
+    <x:t>Item_Wand_1</x:t>
+  </x:si>
+  <x:si>
     <x:t>DropItem</x:t>
   </x:si>
   <x:si>
     <x:t>필드 채집용 옥수수</x:t>
   </x:si>
   <x:si>
-    <x:t>ManaPoints</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Wand_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>체력을 회복한다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2DPrefab/DropItem_ManaBallBlue</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2DPrefab/DropItem_ManaBallPink</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Harvest</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10,1000</x:t>
-  </x:si>
-  <x:si>
-    <x:t>드랍된 금화</x:t>
-  </x:si>
-  <x:si>
-    <x:t>파랑경험치볼</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>주황경험치볼</x:t>
-  </x:si>
-  <x:si>
-    <x:t>고급지팡이</x:t>
-  </x:si>
-  <x:si>
-    <x:t>소량 경험치</x:t>
-  </x:si>
-  <x:si>
-    <x:t>분홍경험치볼</x:t>
-  </x:si>
-  <x:si>
-    <x:t>중량 경험치</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10,100</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대량 경험치</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>int[]</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Exp</x:t>
-  </x:si>
-  <x:si>
-    <x:t>감자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>금화</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>int</x:t>
-  </x:si>
-  <x:si>
-    <x:t>하트</x:t>
-  </x:si>
-  <x:si>
-    <x:t>상자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>옥수수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>지팡이</x:t>
-  </x:si>
-  <x:si>
-    <x:t>마나량</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Wand_DmgUp_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>공격력과 이동속도가 대폭 증가한다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Wand_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_ManaBallPink_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dropItem_chest_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_ManaBallBlue_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>공격력과 이동속도가 소량 증가한다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dropItem_heart_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Chest_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Gold_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Heart_1</x:t>
+    <x:t>2DPrefab/DropItem_WandDmgUp</x:t>
   </x:si>
   <x:si>
     <x:t>dropItem_manaballorange_1</x:t>
   </x:si>
   <x:si>
-    <x:t>2DPrefab/DropItem_WandDmgUp</x:t>
-  </x:si>
-  <x:si>
     <x:t>dropItem_wand_dmgup_1</x:t>
   </x:si>
   <x:si>
+    <x:t>dropItem_manaballpink_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2DPrefab/DropItem_Wand</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2DPrefab/Harvest_Corn</x:t>
+  </x:si>
+  <x:si>
     <x:t>2DPrefab/DropItem_Gold</x:t>
   </x:si>
   <x:si>
+    <x:t>dropItem_manaballblue_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2DPrefab/DropItem_Chest</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2DPrefab/DropItem_Heart</x:t>
+  </x:si>
+  <x:si>
     <x:t>Item_ManaBallOrange_1</x:t>
   </x:si>
   <x:si>
-    <x:t>2DPrefab/Harvest_Corn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dropItem_manaballblue_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2DPrefab/DropItem_Heart</x:t>
-  </x:si>
-  <x:si>
     <x:t>Icon/Icon_Wand_DmgUp_1</x:t>
   </x:si>
   <x:si>
-    <x:t>2DPrefab/DropItem_Wand</x:t>
-  </x:si>
-  <x:si>
     <x:t>2DPrefab/Harvest_Potato</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dropItem_manaballpink_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2DPrefab/DropItem_Chest</x:t>
-  </x:si>
-  <x:si>
-    <x:t>harv_potate_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Heart_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>우선 프리팹으로 구현하자!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Chest_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Potato_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dropItem_wand_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DropItemDataId</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FieldObjectType</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dropItem_gold_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>몬스터 설명 (도감용)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>랜덤한 이벤트가 발생한다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DropCountRange</x:t>
-  </x:si>
-  <x:si>
-    <x:t>데미지증가량</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이속증가량</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HealAmount</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DmgAmount</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1138,68 +1138,68 @@
   <x:sheetData>
     <x:row r="1" spans="1:12" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>5</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B1" s="1"/>
       <x:c r="C1" s="1"/>
       <x:c r="D1" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E1" s="18"/>
       <x:c r="F1" s="18"/>
       <x:c r="G1" s="2"/>
       <x:c r="H1" s="2" t="s">
-        <x:v>70</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="I1" s="3" t="s">
-        <x:v>43</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="J1" s="3" t="s">
-        <x:v>3</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="K1" s="3" t="s">
-        <x:v>80</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="L1" s="3" t="s">
-        <x:v>81</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:12" ht="13.199999999999999">
       <x:c r="A2" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E2" s="18" t="s">
-        <x:v>33</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F2" s="18" t="s">
-        <x:v>29</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G2" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H2" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I2" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="J2" s="3" t="s">
-        <x:v>38</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="K2" s="3" t="s">
-        <x:v>1</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="L2" s="3" t="s">
-        <x:v>1</x:v>
+        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:12" s="13" customFormat="1" ht="15.75" customHeight="1">
@@ -1207,61 +1207,61 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B3" s="12" t="s">
-        <x:v>75</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C3" s="12" t="s">
-        <x:v>23</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D3" s="12" t="s">
-        <x:v>6</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E3" s="19" t="s">
-        <x:v>79</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F3" s="19" t="s">
-        <x:v>74</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G3" s="14" t="s">
-        <x:v>7</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="H3" s="14" t="s">
-        <x:v>11</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="I3" s="15" t="s">
-        <x:v>14</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="J3" s="13" t="s">
-        <x:v>82</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K3" s="13" t="s">
-        <x:v>83</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="L3" s="13" t="s">
-        <x:v>0</x:v>
+        <x:v>57</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A4" s="4" t="s">
-        <x:v>10</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B4" s="4" t="s">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C4" s="4" t="s">
-        <x:v>41</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D4" s="4" t="s">
-        <x:v>13</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="E4" s="20" t="s">
-        <x:v>30</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F4" s="20" t="s">
-        <x:v>9</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="G4" s="5"/>
       <x:c r="H4" s="5" t="s">
-        <x:v>60</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="I4" s="16"/>
       <x:c r="J4" s="5"/>
@@ -1276,28 +1276,28 @@
     </x:row>
     <x:row r="5" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A5" s="6" t="s">
-        <x:v>76</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B5" s="6" t="s">
-        <x:v>12</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C5" s="6" t="s">
-        <x:v>36</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D5" s="6" t="s">
-        <x:v>21</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E5" s="21" t="s">
-        <x:v>20</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F5" s="21" t="s">
-        <x:v>8</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="G5" s="5" t="s">
-        <x:v>53</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="H5" s="5" t="s">
-        <x:v>58</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="I5" s="5"/>
       <x:c r="J5" s="5"/>
@@ -1312,26 +1312,26 @@
     </x:row>
     <x:row r="6" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A6" s="27" t="s">
-        <x:v>68</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B6" s="27" t="s">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C6" s="4" t="s">
-        <x:v>35</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D6" s="4" t="s">
-        <x:v>4</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E6" s="20" t="s">
-        <x:v>30</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F6" s="26" t="s">
-        <x:v>72</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="G6" s="5"/>
       <x:c r="H6" s="28" t="s">
-        <x:v>65</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="I6" s="5"/>
       <x:c r="J6" s="5"/>
@@ -1346,24 +1346,24 @@
     </x:row>
     <x:row r="7" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A7" s="6" t="s">
-        <x:v>61</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B7" s="6" t="s">
-        <x:v>34</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C7" s="7" t="s">
-        <x:v>22</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D7" s="7" t="s">
-        <x:v>26</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="E7" s="22"/>
       <x:c r="F7" s="22" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="G7" s="5"/>
       <x:c r="H7" s="5" t="s">
-        <x:v>17</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="I7" s="5">
         <x:v>10</x:v>
@@ -1380,24 +1380,24 @@
     </x:row>
     <x:row r="8" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A8" s="6" t="s">
-        <x:v>55</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B8" s="6" t="s">
-        <x:v>34</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C8" s="7" t="s">
-        <x:v>24</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D8" s="7" t="s">
-        <x:v>28</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E8" s="22"/>
       <x:c r="F8" s="22" t="s">
-        <x:v>59</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="G8" s="5"/>
       <x:c r="H8" s="5" t="s">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I8" s="5">
         <x:v>50</x:v>
@@ -1414,24 +1414,24 @@
     </x:row>
     <x:row r="9" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A9" s="6" t="s">
-        <x:v>66</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B9" s="6" t="s">
-        <x:v>34</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E9" s="18"/>
       <x:c r="F9" s="18" t="s">
-        <x:v>47</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="G9" s="5"/>
       <x:c r="H9" s="5" t="s">
-        <x:v>18</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="I9" s="5">
         <x:v>100</x:v>
@@ -1448,26 +1448,26 @@
     </x:row>
     <x:row r="10" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A10" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B10" s="6" t="s">
-        <x:v>12</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="E10" s="18"/>
       <x:c r="F10" s="18" t="s">
-        <x:v>69</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="G10" s="5" t="s">
-        <x:v>54</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="H10" s="5" t="s">
-        <x:v>62</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="I10" s="5"/>
       <x:c r="J10" s="5">
@@ -1484,26 +1484,26 @@
     </x:row>
     <x:row r="11" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A11" s="7" t="s">
-        <x:v>73</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B11" s="6" t="s">
-        <x:v>12</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C11" s="7" t="s">
-        <x:v>42</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D11" s="7" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E11" s="22"/>
       <x:c r="F11" s="22" t="s">
-        <x:v>15</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="G11" s="5" t="s">
-        <x:v>46</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="H11" s="5" t="s">
-        <x:v>64</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="I11" s="5"/>
       <x:c r="J11" s="5"/>
@@ -1522,26 +1522,26 @@
     </x:row>
     <x:row r="12" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A12" s="4" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B12" s="6" t="s">
-        <x:v>12</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C12" s="4" t="s">
-        <x:v>40</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="D12" s="4" t="s">
-        <x:v>78</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E12" s="20"/>
       <x:c r="F12" s="20" t="s">
-        <x:v>71</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="G12" s="5" t="s">
-        <x:v>52</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="H12" s="5" t="s">
-        <x:v>67</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="I12" s="5"/>
       <x:c r="J12" s="5"/>
@@ -1556,26 +1556,26 @@
     </x:row>
     <x:row r="13" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A13" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B13" s="6" t="s">
-        <x:v>12</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E13" s="18"/>
       <x:c r="F13" s="18" t="s">
-        <x:v>44</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="G13" s="5" t="s">
-        <x:v>63</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="H13" s="5" t="s">
-        <x:v>56</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="I13" s="5"/>
       <x:c r="J13" s="5"/>

--- a/JsonConverter/ExcelFiles/DNFieldObject.xlsx
+++ b/JsonConverter/ExcelFiles/DNFieldObject.xlsx
@@ -21,256 +21,256 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="84">
   <x:si>
+    <x:t>Icon/Icon_Gold_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Heart_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_ManaBallPink_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>공격력과 이동속도가 소량 증가한다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Wand_DmgUp_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_ManaBallBlue_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Wand_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dropItem_chest_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Chest_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>공격력과 이동속도가 대폭 증가한다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dropItem_heart_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>힐량</x:t>
+  </x:si>
+  <x:si>
+    <x:t>금화</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>지팡이</x:t>
+  </x:si>
+  <x:si>
+    <x:t>옥수수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>상자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Exp</x:t>
+  </x:si>
+  <x:si>
+    <x:t>감자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>하트</x:t>
+  </x:si>
+  <x:si>
+    <x:t>마나량</x:t>
+  </x:si>
+  <x:si>
+    <x:t>고급지팡이</x:t>
+  </x:si>
+  <x:si>
+    <x:t>드랍된 금화</x:t>
+  </x:si>
+  <x:si>
+    <x:t>소량 경험치</x:t>
+  </x:si>
+  <x:si>
+    <x:t>int[]</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10,1000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10,100</x:t>
+  </x:si>
+  <x:si>
+    <x:t>분홍경험치볼</x:t>
+  </x:si>
+  <x:si>
+    <x:t>파랑경험치볼</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이속증가량</x:t>
+  </x:si>
+  <x:si>
+    <x:t>중량 경험치</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대량 경험치</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>데미지증가량</x:t>
+  </x:si>
+  <x:si>
+    <x:t>float</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>주황경험치볼</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Harvest</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Chest_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Heart_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dropItem_gold_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>harv_potate_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>우선 프리팹으로 구현하자!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DropItemDataId</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dropItem_wand_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Potato_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DropCountRange</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FieldObjectType</x:t>
+  </x:si>
+  <x:si>
+    <x:t>랜덤한 이벤트가 발생한다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>몬스터 설명 (도감용)</x:t>
+  </x:si>
+  <x:si>
     <x:t>2DPrefab/DropItem_ManaBallOrange</x:t>
   </x:si>
   <x:si>
+    <x:t>캐릭터 고유 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SpeedAmount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>필드 채집용 옥수수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Wand_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>체력을 회복한다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>harv_corn_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>필드 채집용 감자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DmgAmount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PrefabPath</x:t>
+  </x:si>
+  <x:si>
     <x:t>HealAmount</x:t>
   </x:si>
   <x:si>
-    <x:t>DmgAmount</x:t>
-  </x:si>
-  <x:si>
-    <x:t>분홍경험치볼</x:t>
-  </x:si>
-  <x:si>
-    <x:t>드랍된 금화</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10,100</x:t>
-  </x:si>
-  <x:si>
-    <x:t>고급지팡이</x:t>
-  </x:si>
-  <x:si>
-    <x:t>소량 경험치</x:t>
-  </x:si>
-  <x:si>
-    <x:t>중량 경험치</x:t>
-  </x:si>
-  <x:si>
-    <x:t>float</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10,1000</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Harvest</x:t>
-  </x:si>
-  <x:si>
-    <x:t>주황경험치볼</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>파랑경험치볼</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대량 경험치</x:t>
-  </x:si>
-  <x:si>
-    <x:t>int[]</x:t>
-  </x:si>
-  <x:si>
-    <x:t>데미지증가량</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이속증가량</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dropItem_wand_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Heart_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>harv_potate_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FieldObjectType</x:t>
-  </x:si>
-  <x:si>
-    <x:t>몬스터 설명 (도감용)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>랜덤한 이벤트가 발생한다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DropCountRange</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DropItemDataId</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dropItem_gold_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>우선 프리팹으로 구현하자!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Chest_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Potato_1</x:t>
+    <x:t>Item_Gold_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Corn_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IconPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DropItem</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ManaPoints</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2DPrefab/DropItem_ManaBallBlue</x:t>
   </x:si>
   <x:si>
     <x:t>2DPrefab/DropItem_ManaBallPink</x:t>
   </x:si>
   <x:si>
-    <x:t>2DPrefab/DropItem_ManaBallBlue</x:t>
-  </x:si>
-  <x:si>
-    <x:t>금화</x:t>
-  </x:si>
-  <x:si>
-    <x:t>감자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>하트</x:t>
-  </x:si>
-  <x:si>
-    <x:t>마나량</x:t>
-  </x:si>
-  <x:si>
-    <x:t>지팡이</x:t>
-  </x:si>
-  <x:si>
-    <x:t>int</x:t>
-  </x:si>
-  <x:si>
-    <x:t>상자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>옥수수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Exp</x:t>
-  </x:si>
-  <x:si>
-    <x:t>힐량</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dropItem_heart_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dropItem_chest_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Wand_DmgUp_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_ManaBallPink_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>공격력과 이동속도가 대폭 증가한다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Wand_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_ManaBallBlue_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>공격력과 이동속도가 소량 증가한다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Gold_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Chest_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Heart_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SpeedAmount</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 고유 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Corn_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>harv_corn_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IconPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>필드 채집용 감자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Gold_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ManaPoints</x:t>
-  </x:si>
-  <x:si>
-    <x:t>체력을 회복한다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PrefabPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Wand_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DropItem</x:t>
-  </x:si>
-  <x:si>
-    <x:t>필드 채집용 옥수수</x:t>
+    <x:t>dropItem_manaballorange_1</x:t>
   </x:si>
   <x:si>
     <x:t>2DPrefab/DropItem_WandDmgUp</x:t>
   </x:si>
   <x:si>
-    <x:t>dropItem_manaballorange_1</x:t>
+    <x:t>2DPrefab/DropItem_Chest</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2DPrefab/DropItem_Heart</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2DPrefab/Harvest_Corn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dropItem_manaballpink_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2DPrefab/DropItem_Wand</x:t>
   </x:si>
   <x:si>
     <x:t>dropItem_wand_dmgup_1</x:t>
   </x:si>
   <x:si>
-    <x:t>dropItem_manaballpink_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2DPrefab/DropItem_Wand</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2DPrefab/Harvest_Corn</x:t>
+    <x:t>dropItem_manaballblue_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2DPrefab/Harvest_Potato</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Wand_DmgUp_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_ManaBallOrange_1</x:t>
   </x:si>
   <x:si>
     <x:t>2DPrefab/DropItem_Gold</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dropItem_manaballblue_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2DPrefab/DropItem_Chest</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2DPrefab/DropItem_Heart</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_ManaBallOrange_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Wand_DmgUp_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2DPrefab/Harvest_Potato</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1138,130 +1138,130 @@
   <x:sheetData>
     <x:row r="1" spans="1:12" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B1" s="1"/>
       <x:c r="C1" s="1"/>
       <x:c r="D1" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E1" s="18"/>
       <x:c r="F1" s="18"/>
       <x:c r="G1" s="2"/>
       <x:c r="H1" s="2" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="I1" s="3" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="J1" s="3" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="K1" s="3" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="L1" s="3" t="s">
         <x:v>30</x:v>
-      </x:c>
-      <x:c r="I1" s="3" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="J1" s="3" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="K1" s="3" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="L1" s="3" t="s">
-        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:12" ht="13.199999999999999">
       <x:c r="A2" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C2" s="1" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D2" s="1" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="E2" s="18" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="F2" s="18" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="G2" s="1" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="H2" s="1" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="I2" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C2" s="1" t="s">
+      <x:c r="J2" s="3" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="D2" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="E2" s="18" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F2" s="18" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="G2" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="H2" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="I2" s="1" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="J2" s="3" t="s">
-        <x:v>41</x:v>
-      </x:c>
       <x:c r="K2" s="3" t="s">
-        <x:v>9</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="L2" s="3" t="s">
-        <x:v>9</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:12" s="13" customFormat="1" ht="15.75" customHeight="1">
       <x:c r="A3" s="12" t="s">
-        <x:v>37</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B3" s="12" t="s">
-        <x:v>24</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C3" s="12" t="s">
-        <x:v>10</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D3" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E3" s="19" t="s">
-        <x:v>27</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="F3" s="19" t="s">
-        <x:v>28</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="G3" s="14" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="H3" s="14" t="s">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="H3" s="14" t="s">
-        <x:v>67</x:v>
-      </x:c>
       <x:c r="I3" s="15" t="s">
-        <x:v>65</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="J3" s="13" t="s">
-        <x:v>1</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="K3" s="13" t="s">
-        <x:v>2</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="L3" s="13" t="s">
-        <x:v>57</x:v>
+        <x:v>54</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A4" s="4" t="s">
-        <x:v>61</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B4" s="4" t="s">
-        <x:v>12</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C4" s="4" t="s">
-        <x:v>43</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D4" s="4" t="s">
-        <x:v>70</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E4" s="20" t="s">
-        <x:v>5</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F4" s="20" t="s">
-        <x:v>60</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="G4" s="5"/>
       <x:c r="H4" s="5" t="s">
-        <x:v>76</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="I4" s="16"/>
       <x:c r="J4" s="5"/>
@@ -1276,28 +1276,28 @@
     </x:row>
     <x:row r="5" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A5" s="6" t="s">
-        <x:v>29</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B5" s="6" t="s">
-        <x:v>69</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C5" s="6" t="s">
-        <x:v>35</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D5" s="6" t="s">
-        <x:v>4</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E5" s="21" t="s">
-        <x:v>11</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="F5" s="21" t="s">
         <x:v>64</x:v>
       </x:c>
       <x:c r="G5" s="5" t="s">
-        <x:v>54</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H5" s="5" t="s">
-        <x:v>77</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="I5" s="5"/>
       <x:c r="J5" s="5"/>
@@ -1312,26 +1312,26 @@
     </x:row>
     <x:row r="6" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A6" s="27" t="s">
-        <x:v>23</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B6" s="27" t="s">
-        <x:v>12</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C6" s="4" t="s">
-        <x:v>36</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D6" s="4" t="s">
-        <x:v>63</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E6" s="20" t="s">
-        <x:v>5</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F6" s="26" t="s">
-        <x:v>32</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="G6" s="5"/>
       <x:c r="H6" s="28" t="s">
-        <x:v>83</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="I6" s="5"/>
       <x:c r="J6" s="5"/>
@@ -1346,24 +1346,24 @@
     </x:row>
     <x:row r="7" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A7" s="6" t="s">
-        <x:v>78</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B7" s="6" t="s">
-        <x:v>44</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C7" s="7" t="s">
-        <x:v>15</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D7" s="7" t="s">
-        <x:v>7</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E7" s="22"/>
       <x:c r="F7" s="22" t="s">
-        <x:v>52</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="G7" s="5"/>
       <x:c r="H7" s="5" t="s">
-        <x:v>34</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="I7" s="5">
         <x:v>10</x:v>
@@ -1380,24 +1380,24 @@
     </x:row>
     <x:row r="8" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A8" s="6" t="s">
-        <x:v>72</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B8" s="6" t="s">
-        <x:v>44</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C8" s="7" t="s">
-        <x:v>13</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D8" s="7" t="s">
-        <x:v>8</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E8" s="22"/>
       <x:c r="F8" s="22" t="s">
-        <x:v>81</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="G8" s="5"/>
       <x:c r="H8" s="5" t="s">
-        <x:v>0</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="I8" s="5">
         <x:v>50</x:v>
@@ -1414,24 +1414,24 @@
     </x:row>
     <x:row r="9" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A9" s="6" t="s">
-        <x:v>74</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B9" s="6" t="s">
-        <x:v>44</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>3</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E9" s="18"/>
       <x:c r="F9" s="18" t="s">
-        <x:v>49</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="G9" s="5"/>
       <x:c r="H9" s="5" t="s">
-        <x:v>33</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="I9" s="5">
         <x:v>100</x:v>
@@ -1448,26 +1448,26 @@
     </x:row>
     <x:row r="10" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A10" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B10" s="6" t="s">
-        <x:v>69</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="E10" s="18"/>
       <x:c r="F10" s="18" t="s">
-        <x:v>22</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G10" s="5" t="s">
-        <x:v>56</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H10" s="5" t="s">
-        <x:v>80</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="I10" s="5"/>
       <x:c r="J10" s="5">
@@ -1484,31 +1484,31 @@
     </x:row>
     <x:row r="11" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A11" s="7" t="s">
-        <x:v>21</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B11" s="6" t="s">
-        <x:v>69</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C11" s="7" t="s">
-        <x:v>40</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D11" s="7" t="s">
-        <x:v>53</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="E11" s="22"/>
       <x:c r="F11" s="22" t="s">
-        <x:v>68</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="G11" s="5" t="s">
-        <x:v>51</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H11" s="5" t="s">
-        <x:v>75</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="I11" s="5"/>
       <x:c r="J11" s="5"/>
       <x:c r="K11" s="5">
-        <x:v>50</x:v>
+        <x:v>0.5</x:v>
       </x:c>
       <x:c r="L11" s="5">
         <x:v>1</x:v>
@@ -1522,26 +1522,26 @@
     </x:row>
     <x:row r="12" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A12" s="4" t="s">
-        <x:v>47</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B12" s="6" t="s">
-        <x:v>69</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C12" s="4" t="s">
-        <x:v>42</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D12" s="4" t="s">
-        <x:v>26</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E12" s="20"/>
       <x:c r="F12" s="20" t="s">
-        <x:v>31</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G12" s="5" t="s">
-        <x:v>55</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="H12" s="5" t="s">
-        <x:v>79</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="I12" s="5"/>
       <x:c r="J12" s="5"/>
@@ -1556,34 +1556,34 @@
     </x:row>
     <x:row r="13" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A13" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B13" s="6" t="s">
-        <x:v>69</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>6</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E13" s="18"/>
       <x:c r="F13" s="18" t="s">
-        <x:v>48</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="G13" s="5" t="s">
-        <x:v>82</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="H13" s="5" t="s">
-        <x:v>71</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="I13" s="5"/>
       <x:c r="J13" s="5"/>
       <x:c r="K13" s="5">
-        <x:v>200</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="L13" s="5">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="M13" s="5"/>
       <x:c r="N13" s="5"/>

--- a/JsonConverter/ExcelFiles/DNFieldObject.xlsx
+++ b/JsonConverter/ExcelFiles/DNFieldObject.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <x:bookViews>
-    <x:workbookView xWindow="0" yWindow="0" windowWidth="22788" windowHeight="8520"/>
+    <x:workbookView xWindow="0" yWindow="0" windowWidth="16332" windowHeight="6744"/>
   </x:bookViews>
   <x:sheets>
     <x:sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId4"/>
@@ -21,19 +21,178 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="84">
   <x:si>
+    <x:t>2DPrefab/DropItem_ManaBallPink</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2DPrefab/DropItem_ManaBallBlue</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DmgAmount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>필드 채집용 감자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PrefabPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 고유 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IconPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>float</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2DPrefab/DropItem_ManaBallOrange</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dropItem_manaballpink_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2DPrefab/DropItem_Gold</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2DPrefab/DropItem_Heart</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dropItem_manaballblue_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2DPrefab/Harvest_Corn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2DPrefab/DropItem_Chest</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2DPrefab/Harvest_Potato</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_ManaBallOrange_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dropItem_wand_dmgup_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2DPrefab/DropItem_Wand</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Wand_DmgUp_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>필드 채집용 옥수수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>체력을 회복한다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>harv_corn_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Wand_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SpeedAmount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HealAmount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ManaPoints</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DropItem</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Gold_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Corn_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>int[]</x:t>
+  </x:si>
+  <x:si>
+    <x:t>분홍경험치볼</x:t>
+  </x:si>
+  <x:si>
+    <x:t>중량 경험치</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이속증가량</x:t>
+  </x:si>
+  <x:si>
+    <x:t>데미지증가량</x:t>
+  </x:si>
+  <x:si>
+    <x:t>파랑경험치볼</x:t>
+  </x:si>
+  <x:si>
+    <x:t>고급지팡이</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10,100</x:t>
+  </x:si>
+  <x:si>
+    <x:t>드랍된 금화</x:t>
+  </x:si>
+  <x:si>
+    <x:t>소량 경험치</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10,1000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대량 경험치</x:t>
+  </x:si>
+  <x:si>
+    <x:t>주황경험치볼</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Harvest</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Heart_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Wand_DmgUp_1</x:t>
+  </x:si>
+  <x:si>
     <x:t>Icon/Icon_Gold_1</x:t>
   </x:si>
   <x:si>
-    <x:t>Icon/Icon_Heart_1</x:t>
-  </x:si>
-  <x:si>
     <x:t>Item_ManaBallPink_1</x:t>
   </x:si>
   <x:si>
-    <x:t>공격력과 이동속도가 소량 증가한다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Wand_DmgUp_1</x:t>
+    <x:t>dropItem_chest_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>공격력과 이동속도가 대폭 증가한다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dropItem_heart_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Chest_1</x:t>
   </x:si>
   <x:si>
     <x:t>Item_ManaBallBlue_1</x:t>
@@ -42,103 +201,34 @@
     <x:t>Icon/Icon_Wand_1</x:t>
   </x:si>
   <x:si>
-    <x:t>dropItem_chest_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Chest_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>공격력과 이동속도가 대폭 증가한다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dropItem_heart_1</x:t>
-  </x:si>
-  <x:si>
     <x:t>힐량</x:t>
   </x:si>
   <x:si>
+    <x:t>옥수수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>감자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>하트</x:t>
+  </x:si>
+  <x:si>
+    <x:t>지팡이</x:t>
+  </x:si>
+  <x:si>
+    <x:t>마나량</x:t>
+  </x:si>
+  <x:si>
     <x:t>금화</x:t>
   </x:si>
   <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>int</x:t>
-  </x:si>
-  <x:si>
-    <x:t>지팡이</x:t>
-  </x:si>
-  <x:si>
-    <x:t>옥수수</x:t>
-  </x:si>
-  <x:si>
     <x:t>상자</x:t>
   </x:si>
   <x:si>
     <x:t>Exp</x:t>
   </x:si>
   <x:si>
-    <x:t>감자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>하트</x:t>
-  </x:si>
-  <x:si>
-    <x:t>마나량</x:t>
-  </x:si>
-  <x:si>
-    <x:t>고급지팡이</x:t>
-  </x:si>
-  <x:si>
-    <x:t>드랍된 금화</x:t>
-  </x:si>
-  <x:si>
-    <x:t>소량 경험치</x:t>
-  </x:si>
-  <x:si>
-    <x:t>int[]</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10,1000</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10,100</x:t>
-  </x:si>
-  <x:si>
-    <x:t>분홍경험치볼</x:t>
-  </x:si>
-  <x:si>
-    <x:t>파랑경험치볼</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이속증가량</x:t>
-  </x:si>
-  <x:si>
-    <x:t>중량 경험치</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대량 경험치</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>데미지증가량</x:t>
-  </x:si>
-  <x:si>
-    <x:t>float</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>주황경험치볼</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Harvest</x:t>
+    <x:t>harv_potate_1</x:t>
   </x:si>
   <x:si>
     <x:t>Item_Chest_1</x:t>
@@ -147,130 +237,40 @@
     <x:t>Item_Heart_1</x:t>
   </x:si>
   <x:si>
+    <x:t>우선 프리팹으로 구현하자!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DropItemDataId</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dropItem_wand_1</x:t>
+  </x:si>
+  <x:si>
     <x:t>dropItem_gold_1</x:t>
   </x:si>
   <x:si>
-    <x:t>harv_potate_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>우선 프리팹으로 구현하자!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DropItemDataId</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dropItem_wand_1</x:t>
+    <x:t>DropCountRange</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FieldObjectType</x:t>
+  </x:si>
+  <x:si>
+    <x:t>랜덤한 이벤트가 발생한다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>몬스터 설명 (도감용)</x:t>
   </x:si>
   <x:si>
     <x:t>Item_Potato_1</x:t>
   </x:si>
   <x:si>
-    <x:t>DropCountRange</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FieldObjectType</x:t>
-  </x:si>
-  <x:si>
-    <x:t>랜덤한 이벤트가 발생한다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>몬스터 설명 (도감용)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2DPrefab/DropItem_ManaBallOrange</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 고유 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SpeedAmount</x:t>
-  </x:si>
-  <x:si>
-    <x:t>필드 채집용 옥수수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Wand_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>체력을 회복한다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>harv_corn_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>필드 채집용 감자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DmgAmount</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PrefabPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HealAmount</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Gold_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Corn_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IconPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DropItem</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ManaPoints</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2DPrefab/DropItem_ManaBallBlue</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2DPrefab/DropItem_ManaBallPink</x:t>
-  </x:si>
-  <x:si>
     <x:t>dropItem_manaballorange_1</x:t>
   </x:si>
   <x:si>
     <x:t>2DPrefab/DropItem_WandDmgUp</x:t>
   </x:si>
   <x:si>
-    <x:t>2DPrefab/DropItem_Chest</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2DPrefab/DropItem_Heart</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2DPrefab/Harvest_Corn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dropItem_manaballpink_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2DPrefab/DropItem_Wand</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dropItem_wand_dmgup_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dropItem_manaballblue_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2DPrefab/Harvest_Potato</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Wand_DmgUp_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_ManaBallOrange_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2DPrefab/DropItem_Gold</x:t>
+    <x:t>공격력과 이동속도가 소폭 증가한다</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1138,68 +1138,68 @@
   <x:sheetData>
     <x:row r="1" spans="1:12" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="B1" s="1"/>
       <x:c r="C1" s="1"/>
       <x:c r="D1" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="E1" s="18"/>
       <x:c r="F1" s="18"/>
       <x:c r="G1" s="2"/>
       <x:c r="H1" s="2" t="s">
-        <x:v>44</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="I1" s="3" t="s">
-        <x:v>21</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="J1" s="3" t="s">
-        <x:v>11</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="K1" s="3" t="s">
-        <x:v>34</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="L1" s="3" t="s">
-        <x:v>30</x:v>
+        <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:12" ht="13.199999999999999">
       <x:c r="A2" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C2" s="1" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="D2" s="1" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="E2" s="18" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="C2" s="1" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="D2" s="1" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="E2" s="18" t="s">
-        <x:v>25</x:v>
-      </x:c>
       <x:c r="F2" s="18" t="s">
-        <x:v>36</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="G2" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="H2" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="I2" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="J2" s="3" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="K2" s="3" t="s">
-        <x:v>35</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="L2" s="3" t="s">
-        <x:v>35</x:v>
+        <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:12" s="13" customFormat="1" ht="15.75" customHeight="1">
@@ -1207,61 +1207,61 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B3" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C3" s="12" t="s">
-        <x:v>33</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D3" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E3" s="19" t="s">
-        <x:v>48</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="F3" s="19" t="s">
-        <x:v>45</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="G3" s="14" t="s">
-        <x:v>66</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="H3" s="14" t="s">
-        <x:v>62</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="I3" s="15" t="s">
-        <x:v>68</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="J3" s="13" t="s">
-        <x:v>63</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="K3" s="13" t="s">
-        <x:v>61</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="L3" s="13" t="s">
-        <x:v>54</x:v>
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A4" s="4" t="s">
-        <x:v>59</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B4" s="4" t="s">
-        <x:v>39</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C4" s="4" t="s">
-        <x:v>16</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="D4" s="4" t="s">
-        <x:v>55</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E4" s="20" t="s">
-        <x:v>27</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="F4" s="20" t="s">
-        <x:v>65</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="G4" s="5"/>
       <x:c r="H4" s="5" t="s">
-        <x:v>75</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="I4" s="16"/>
       <x:c r="J4" s="5"/>
@@ -1276,28 +1276,28 @@
     </x:row>
     <x:row r="5" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A5" s="6" t="s">
-        <x:v>42</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B5" s="6" t="s">
-        <x:v>67</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C5" s="6" t="s">
-        <x:v>12</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D5" s="6" t="s">
-        <x:v>23</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E5" s="21" t="s">
-        <x:v>26</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="F5" s="21" t="s">
-        <x:v>64</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="G5" s="5" t="s">
-        <x:v>0</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="H5" s="5" t="s">
-        <x:v>83</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="I5" s="5"/>
       <x:c r="J5" s="5"/>
@@ -1312,26 +1312,26 @@
     </x:row>
     <x:row r="6" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A6" s="27" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="B6" s="27" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="C6" s="4" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="D6" s="4" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E6" s="20" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="B6" s="27" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="C6" s="4" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="D6" s="4" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="E6" s="20" t="s">
-        <x:v>27</x:v>
-      </x:c>
       <x:c r="F6" s="26" t="s">
-        <x:v>47</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="G6" s="5"/>
       <x:c r="H6" s="28" t="s">
-        <x:v>80</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="I6" s="5"/>
       <x:c r="J6" s="5"/>
@@ -1346,24 +1346,24 @@
     </x:row>
     <x:row r="7" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A7" s="6" t="s">
-        <x:v>79</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B7" s="6" t="s">
-        <x:v>18</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C7" s="7" t="s">
-        <x:v>29</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D7" s="7" t="s">
-        <x:v>24</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E7" s="22"/>
       <x:c r="F7" s="22" t="s">
-        <x:v>5</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="G7" s="5"/>
       <x:c r="H7" s="5" t="s">
-        <x:v>69</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I7" s="5">
         <x:v>10</x:v>
@@ -1380,24 +1380,24 @@
     </x:row>
     <x:row r="8" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A8" s="6" t="s">
-        <x:v>71</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B8" s="6" t="s">
-        <x:v>18</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C8" s="7" t="s">
-        <x:v>37</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D8" s="7" t="s">
-        <x:v>31</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E8" s="22"/>
       <x:c r="F8" s="22" t="s">
-        <x:v>82</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="G8" s="5"/>
       <x:c r="H8" s="5" t="s">
-        <x:v>52</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I8" s="5">
         <x:v>50</x:v>
@@ -1414,24 +1414,24 @@
     </x:row>
     <x:row r="9" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A9" s="6" t="s">
-        <x:v>76</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B9" s="6" t="s">
-        <x:v>18</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E9" s="18"/>
       <x:c r="F9" s="18" t="s">
-        <x:v>2</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="G9" s="5"/>
       <x:c r="H9" s="5" t="s">
-        <x:v>70</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I9" s="5">
         <x:v>100</x:v>
@@ -1448,26 +1448,26 @@
     </x:row>
     <x:row r="10" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A10" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B10" s="6" t="s">
-        <x:v>67</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E10" s="18"/>
       <x:c r="F10" s="18" t="s">
-        <x:v>41</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="G10" s="5" t="s">
-        <x:v>1</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="H10" s="5" t="s">
-        <x:v>74</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="I10" s="5"/>
       <x:c r="J10" s="5">
@@ -1484,26 +1484,26 @@
     </x:row>
     <x:row r="11" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A11" s="7" t="s">
-        <x:v>46</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B11" s="6" t="s">
-        <x:v>67</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C11" s="7" t="s">
-        <x:v>15</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="D11" s="7" t="s">
-        <x:v>3</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="E11" s="22"/>
       <x:c r="F11" s="22" t="s">
-        <x:v>57</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="G11" s="5" t="s">
-        <x:v>6</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="H11" s="5" t="s">
-        <x:v>77</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="I11" s="5"/>
       <x:c r="J11" s="5"/>
@@ -1522,26 +1522,26 @@
     </x:row>
     <x:row r="12" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A12" s="4" t="s">
-        <x:v>7</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B12" s="6" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C12" s="4" t="s">
         <x:v>67</x:v>
       </x:c>
-      <x:c r="C12" s="4" t="s">
-        <x:v>17</x:v>
-      </x:c>
       <x:c r="D12" s="4" t="s">
-        <x:v>50</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="E12" s="20"/>
       <x:c r="F12" s="20" t="s">
-        <x:v>40</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="G12" s="5" t="s">
-        <x:v>8</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="H12" s="5" t="s">
-        <x:v>73</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="I12" s="5"/>
       <x:c r="J12" s="5"/>
@@ -1556,26 +1556,26 @@
     </x:row>
     <x:row r="13" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A13" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B13" s="6" t="s">
-        <x:v>67</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E13" s="18"/>
       <x:c r="F13" s="18" t="s">
-        <x:v>4</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="G13" s="5" t="s">
-        <x:v>81</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="H13" s="5" t="s">
-        <x:v>72</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="I13" s="5"/>
       <x:c r="J13" s="5"/>
